--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:12</t>
+    <t xml:space="preserve">2026-09-09 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:06</t>
+    <t xml:space="preserve">2026-09-17 14:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:03</t>
+    <t xml:space="preserve">2026-09-23 12:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:32</t>
+    <t xml:space="preserve">2026-10-02 14:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_nuble.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Chillán Viejo</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Ñiquén</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:16</t>
+    <t xml:space="preserve">2026-10-04 08:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:56</t>
+    <t xml:space="preserve">2026-10-05 10:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -680,7 +680,7 @@
         <v>2024</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>960654.12</v>
+        <v>960654.13</v>
       </c>
     </row>
     <row r="11">
@@ -697,7 +697,7 @@
         <v>2024</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>959673.12</v>
+        <v>959673.13</v>
       </c>
     </row>
     <row r="12">
@@ -748,7 +748,7 @@
         <v>2024</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>913319.62</v>
+        <v>913319.63</v>
       </c>
     </row>
     <row r="15">
